--- a/99 - Excels/Open-LPs - pé.xlsx
+++ b/99 - Excels/Open-LPs - pé.xlsx
@@ -1,105 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\feb3ct\Desktop\PyAutomateSAP\98 - Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB11FD9-17B3-4842-AE0D-2475B0A8E9BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>LP</t>
-  </si>
-  <si>
-    <t>LP-048266</t>
-  </si>
-  <si>
-    <t>LP-050665</t>
-  </si>
-  <si>
-    <t>LP-051510</t>
-  </si>
-  <si>
-    <t>LP-051807</t>
-  </si>
-  <si>
-    <t>LP-051809</t>
-  </si>
-  <si>
-    <t>LP-051811</t>
-  </si>
-  <si>
-    <t>LP-052225</t>
-  </si>
-  <si>
-    <t>LP-052397</t>
-  </si>
-  <si>
-    <t>LP-052399</t>
-  </si>
-  <si>
-    <t>LP-053064</t>
-  </si>
-  <si>
-    <t>LP-053109</t>
-  </si>
-  <si>
-    <t>LP-053265</t>
-  </si>
-  <si>
-    <t>LP-054347</t>
-  </si>
-  <si>
-    <t>LP-050726</t>
-  </si>
-  <si>
-    <t>LP-052963</t>
-  </si>
-  <si>
-    <t>LP-054212</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -107,44 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -432,97 +408,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LP-047118</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LP-050253</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LP-050762</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LP-051345</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LP-051352</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LP-051443</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LP-051786</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LP-052186</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LP-052373</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LP-052408</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LP-052709</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LP-052906</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LP-052914</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LP-052977</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LP-053062</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LP-053089</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LP-053471</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LP-053507</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LP-053728</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LP-053895</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LP-053896</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LP-053913</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LP-054010</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LP-054210</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LP-051348</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/99 - Excels/Open-LPs - pé.xlsx
+++ b/99 - Excels/Open-LPs - pé.xlsx
@@ -1,34 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4DC96E-6CD4-4579-BBFA-E2D5475BCD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>LP-050865</t>
+  </si>
+  <si>
+    <t>LP-051402</t>
+  </si>
+  <si>
+    <t>LP-052224</t>
+  </si>
+  <si>
+    <t>LP-053232</t>
+  </si>
+  <si>
+    <t>LP-053830</t>
+  </si>
+  <si>
+    <t>LP-053887</t>
+  </si>
+  <si>
+    <t>LP-053929</t>
+  </si>
+  <si>
+    <t>LP-054987</t>
+  </si>
+  <si>
+    <t>LP-055169</t>
+  </si>
+  <si>
+    <t>LP-055699</t>
+  </si>
+  <si>
+    <t>LP-055767</t>
+  </si>
+  <si>
+    <t>LP-055838</t>
+  </si>
+  <si>
+    <t>LP-055900</t>
+  </si>
+  <si>
+    <t>LP-056053</t>
+  </si>
+  <si>
+    <t>LP-056090</t>
+  </si>
+  <si>
+    <t>LP-056278</t>
+  </si>
+  <si>
+    <t>LP-051140</t>
+  </si>
+  <si>
+    <t>LP-051310</t>
+  </si>
+  <si>
+    <t>LP-053407</t>
+  </si>
+  <si>
+    <t>LP-054907</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +119,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,204 +421,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>LP-047118</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LP-050253</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LP-050762</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LP-051345</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LP-051352</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LP-051443</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>LP-051786</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>LP-052186</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>LP-052373</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>LP-052408</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LP-052709</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>LP-052906</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>LP-052914</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>LP-052977</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>LP-053062</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>LP-053089</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>LP-053471</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LP-053507</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LP-053728</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LP-053895</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>LP-053896</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>LP-053913</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LP-054010</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>LP-054210</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>LP-051348</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/99 - Excels/Open-LPs - pé.xlsx
+++ b/99 - Excels/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4DC96E-6CD4-4579-BBFA-E2D5475BCD7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C40313-753C-408F-8F4B-74BF5703F7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,69 +20,516 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-050865</t>
-  </si>
-  <si>
-    <t>LP-051402</t>
-  </si>
-  <si>
-    <t>LP-052224</t>
-  </si>
-  <si>
-    <t>LP-053232</t>
-  </si>
-  <si>
-    <t>LP-053830</t>
-  </si>
-  <si>
-    <t>LP-053887</t>
-  </si>
-  <si>
-    <t>LP-053929</t>
-  </si>
-  <si>
-    <t>LP-054987</t>
-  </si>
-  <si>
-    <t>LP-055169</t>
-  </si>
-  <si>
-    <t>LP-055699</t>
-  </si>
-  <si>
-    <t>LP-055767</t>
-  </si>
-  <si>
-    <t>LP-055838</t>
-  </si>
-  <si>
-    <t>LP-055900</t>
-  </si>
-  <si>
-    <t>LP-056053</t>
-  </si>
-  <si>
-    <t>LP-056090</t>
-  </si>
-  <si>
-    <t>LP-056278</t>
-  </si>
-  <si>
-    <t>LP-051140</t>
-  </si>
-  <si>
-    <t>LP-051310</t>
-  </si>
-  <si>
-    <t>LP-053407</t>
-  </si>
-  <si>
-    <t>LP-054907</t>
+    <t>LP-050245</t>
+  </si>
+  <si>
+    <t>LP-050761</t>
+  </si>
+  <si>
+    <t>LP-050781</t>
+  </si>
+  <si>
+    <t>LP-051027</t>
+  </si>
+  <si>
+    <t>LP-051031</t>
+  </si>
+  <si>
+    <t>LP-051034</t>
+  </si>
+  <si>
+    <t>LP-051035</t>
+  </si>
+  <si>
+    <t>LP-051046</t>
+  </si>
+  <si>
+    <t>LP-051054</t>
+  </si>
+  <si>
+    <t>LP-051079</t>
+  </si>
+  <si>
+    <t>LP-051141</t>
+  </si>
+  <si>
+    <t>LP-051152</t>
+  </si>
+  <si>
+    <t>LP-051153</t>
+  </si>
+  <si>
+    <t>LP-051154</t>
+  </si>
+  <si>
+    <t>LP-052100</t>
+  </si>
+  <si>
+    <t>LP-052101</t>
+  </si>
+  <si>
+    <t>LP-052237</t>
+  </si>
+  <si>
+    <t>LP-052377</t>
+  </si>
+  <si>
+    <t>LP-052406</t>
+  </si>
+  <si>
+    <t>LP-052677</t>
+  </si>
+  <si>
+    <t>LP-052705</t>
+  </si>
+  <si>
+    <t>LP-052706</t>
+  </si>
+  <si>
+    <t>LP-052708</t>
+  </si>
+  <si>
+    <t>LP-052710</t>
+  </si>
+  <si>
+    <t>LP-052711</t>
+  </si>
+  <si>
+    <t>LP-052744</t>
+  </si>
+  <si>
+    <t>LP-052791</t>
+  </si>
+  <si>
+    <t>LP-052915</t>
+  </si>
+  <si>
+    <t>LP-052919</t>
+  </si>
+  <si>
+    <t>LP-052957</t>
+  </si>
+  <si>
+    <t>LP-053025</t>
+  </si>
+  <si>
+    <t>LP-053052</t>
+  </si>
+  <si>
+    <t>LP-053107</t>
+  </si>
+  <si>
+    <t>LP-053110</t>
+  </si>
+  <si>
+    <t>LP-053211</t>
+  </si>
+  <si>
+    <t>LP-053229</t>
+  </si>
+  <si>
+    <t>LP-053299</t>
+  </si>
+  <si>
+    <t>LP-053412</t>
+  </si>
+  <si>
+    <t>LP-053415</t>
+  </si>
+  <si>
+    <t>LP-053423</t>
+  </si>
+  <si>
+    <t>LP-053429</t>
+  </si>
+  <si>
+    <t>LP-053444</t>
+  </si>
+  <si>
+    <t>LP-053445</t>
+  </si>
+  <si>
+    <t>LP-053508</t>
+  </si>
+  <si>
+    <t>LP-053804</t>
+  </si>
+  <si>
+    <t>LP-053883</t>
+  </si>
+  <si>
+    <t>LP-053893</t>
+  </si>
+  <si>
+    <t>LP-053944</t>
+  </si>
+  <si>
+    <t>LP-053945</t>
+  </si>
+  <si>
+    <t>LP-054204</t>
+  </si>
+  <si>
+    <t>LP-054555</t>
+  </si>
+  <si>
+    <t>LP-054564</t>
+  </si>
+  <si>
+    <t>LP-054573</t>
+  </si>
+  <si>
+    <t>LP-054733</t>
+  </si>
+  <si>
+    <t>LP-054735</t>
+  </si>
+  <si>
+    <t>LP-054826</t>
+  </si>
+  <si>
+    <t>LP-054835</t>
+  </si>
+  <si>
+    <t>LP-054836</t>
+  </si>
+  <si>
+    <t>LP-054906</t>
+  </si>
+  <si>
+    <t>LP-054908</t>
+  </si>
+  <si>
+    <t>LP-054959</t>
+  </si>
+  <si>
+    <t>LP-054961</t>
+  </si>
+  <si>
+    <t>LP-055068</t>
+  </si>
+  <si>
+    <t>LP-055069</t>
+  </si>
+  <si>
+    <t>LP-055077</t>
+  </si>
+  <si>
+    <t>LP-055078</t>
+  </si>
+  <si>
+    <t>LP-055081</t>
+  </si>
+  <si>
+    <t>LP-055082</t>
+  </si>
+  <si>
+    <t>LP-055165</t>
+  </si>
+  <si>
+    <t>LP-055321</t>
+  </si>
+  <si>
+    <t>LP-055322</t>
+  </si>
+  <si>
+    <t>LP-055344</t>
+  </si>
+  <si>
+    <t>LP-055363</t>
+  </si>
+  <si>
+    <t>LP-055370</t>
+  </si>
+  <si>
+    <t>LP-055373</t>
+  </si>
+  <si>
+    <t>LP-055376</t>
+  </si>
+  <si>
+    <t>LP-055398</t>
+  </si>
+  <si>
+    <t>LP-055499</t>
+  </si>
+  <si>
+    <t>LP-055641</t>
+  </si>
+  <si>
+    <t>LP-055662</t>
+  </si>
+  <si>
+    <t>LP-055664</t>
+  </si>
+  <si>
+    <t>LP-055668</t>
+  </si>
+  <si>
+    <t>LP-055669</t>
+  </si>
+  <si>
+    <t>LP-055671</t>
+  </si>
+  <si>
+    <t>LP-055679</t>
+  </si>
+  <si>
+    <t>LP-055686</t>
+  </si>
+  <si>
+    <t>LP-055695</t>
+  </si>
+  <si>
+    <t>LP-055704</t>
+  </si>
+  <si>
+    <t>LP-055705</t>
+  </si>
+  <si>
+    <t>LP-055706</t>
+  </si>
+  <si>
+    <t>LP-055707</t>
+  </si>
+  <si>
+    <t>LP-055708</t>
+  </si>
+  <si>
+    <t>LP-055709</t>
+  </si>
+  <si>
+    <t>LP-055733</t>
+  </si>
+  <si>
+    <t>LP-055734</t>
+  </si>
+  <si>
+    <t>LP-055735</t>
+  </si>
+  <si>
+    <t>LP-055758</t>
+  </si>
+  <si>
+    <t>LP-055766</t>
+  </si>
+  <si>
+    <t>LP-055798</t>
+  </si>
+  <si>
+    <t>LP-055806</t>
+  </si>
+  <si>
+    <t>LP-055839</t>
+  </si>
+  <si>
+    <t>LP-055840</t>
+  </si>
+  <si>
+    <t>LP-055950</t>
+  </si>
+  <si>
+    <t>LP-056039</t>
+  </si>
+  <si>
+    <t>LP-056041</t>
+  </si>
+  <si>
+    <t>LP-056050</t>
+  </si>
+  <si>
+    <t>LP-056052</t>
+  </si>
+  <si>
+    <t>LP-056054</t>
+  </si>
+  <si>
+    <t>LP-056056</t>
+  </si>
+  <si>
+    <t>LP-056057</t>
+  </si>
+  <si>
+    <t>LP-056081</t>
+  </si>
+  <si>
+    <t>LP-056082</t>
+  </si>
+  <si>
+    <t>LP-056084</t>
+  </si>
+  <si>
+    <t>LP-056085</t>
+  </si>
+  <si>
+    <t>LP-056086</t>
+  </si>
+  <si>
+    <t>LP-056087</t>
+  </si>
+  <si>
+    <t>LP-056088</t>
+  </si>
+  <si>
+    <t>LP-056116</t>
+  </si>
+  <si>
+    <t>LP-056121</t>
+  </si>
+  <si>
+    <t>LP-056127</t>
+  </si>
+  <si>
+    <t>LP-056128</t>
+  </si>
+  <si>
+    <t>LP-056134</t>
+  </si>
+  <si>
+    <t>LP-056136</t>
+  </si>
+  <si>
+    <t>LP-056200</t>
+  </si>
+  <si>
+    <t>LP-056282</t>
+  </si>
+  <si>
+    <t>LP-056372</t>
+  </si>
+  <si>
+    <t>LP-056373</t>
+  </si>
+  <si>
+    <t>LP-056378</t>
+  </si>
+  <si>
+    <t>LP-056379</t>
+  </si>
+  <si>
+    <t>LP-056386</t>
+  </si>
+  <si>
+    <t>LP-056387</t>
+  </si>
+  <si>
+    <t>LP-056389</t>
+  </si>
+  <si>
+    <t>LP-056390</t>
+  </si>
+  <si>
+    <t>LP-056404</t>
+  </si>
+  <si>
+    <t>LP-056405</t>
+  </si>
+  <si>
+    <t>LP-056408</t>
+  </si>
+  <si>
+    <t>LP-056409</t>
+  </si>
+  <si>
+    <t>LP-056415</t>
+  </si>
+  <si>
+    <t>LP-056523</t>
+  </si>
+  <si>
+    <t>LP-056624</t>
+  </si>
+  <si>
+    <t>LP-056625</t>
+  </si>
+  <si>
+    <t>LP-056715</t>
+  </si>
+  <si>
+    <t>LP-056718</t>
+  </si>
+  <si>
+    <t>LP-050251</t>
+  </si>
+  <si>
+    <t>LP-052244</t>
+  </si>
+  <si>
+    <t>LP-052627</t>
+  </si>
+  <si>
+    <t>LP-052921</t>
+  </si>
+  <si>
+    <t>LP-053023</t>
+  </si>
+  <si>
+    <t>LP-053055</t>
+  </si>
+  <si>
+    <t>LP-053397</t>
+  </si>
+  <si>
+    <t>LP-053403</t>
+  </si>
+  <si>
+    <t>LP-053406</t>
+  </si>
+  <si>
+    <t>LP-053411</t>
+  </si>
+  <si>
+    <t>LP-053414</t>
+  </si>
+  <si>
+    <t>LP-053424</t>
+  </si>
+  <si>
+    <t>LP-053425</t>
+  </si>
+  <si>
+    <t>LP-053427</t>
+  </si>
+  <si>
+    <t>LP-054173</t>
+  </si>
+  <si>
+    <t>LP-054174</t>
+  </si>
+  <si>
+    <t>LP-054187</t>
+  </si>
+  <si>
+    <t>LP-054356</t>
+  </si>
+  <si>
+    <t>LP-054905</t>
+  </si>
+  <si>
+    <t>LP-054909</t>
+  </si>
+  <si>
+    <t>LP-055366</t>
+  </si>
+  <si>
+    <t>LP-055336</t>
+  </si>
+  <si>
+    <t>LP-055666</t>
+  </si>
+  <si>
+    <t>LP-055677</t>
+  </si>
+  <si>
+    <t>LP-056407</t>
+  </si>
+  <si>
+    <t>LP-056453</t>
   </si>
 </sst>
 </file>
@@ -422,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -437,97 +884,842 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/Open-LPs - pé.xlsx
+++ b/99 - Excels/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F58327-B6E9-4C93-924A-34793C5CF84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A34087-F46E-4444-908A-F871187D3179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,129 +20,306 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-056528</t>
-  </si>
-  <si>
-    <t>LP-056495</t>
-  </si>
-  <si>
-    <t>LP-056414</t>
-  </si>
-  <si>
-    <t>LP-056402</t>
-  </si>
-  <si>
-    <t>LP-056401</t>
-  </si>
-  <si>
-    <t>LP-056374</t>
-  </si>
-  <si>
-    <t>LP-056043</t>
-  </si>
-  <si>
-    <t>LP-056042</t>
-  </si>
-  <si>
-    <t>LP-055952</t>
-  </si>
-  <si>
-    <t>LP-055842</t>
-  </si>
-  <si>
-    <t>LP-055723</t>
-  </si>
-  <si>
-    <t>LP-055684</t>
-  </si>
-  <si>
-    <t>LP-055382</t>
-  </si>
-  <si>
-    <t>LP-055673</t>
-  </si>
-  <si>
-    <t>LP-055672</t>
-  </si>
-  <si>
-    <t>LP-055660</t>
-  </si>
-  <si>
-    <t>LP-055659</t>
-  </si>
-  <si>
-    <t>LP-054464</t>
-  </si>
-  <si>
-    <t>LP-055198</t>
-  </si>
-  <si>
-    <t>LP-055080</t>
-  </si>
-  <si>
-    <t>LP-054911</t>
-  </si>
-  <si>
-    <t>LP-054833</t>
-  </si>
-  <si>
-    <t>LP-054572</t>
-  </si>
-  <si>
-    <t>LP-053438</t>
-  </si>
-  <si>
-    <t>LP-053216</t>
-  </si>
-  <si>
-    <t>LP-053104</t>
-  </si>
-  <si>
-    <t>LP-052947</t>
-  </si>
-  <si>
-    <t>LP-052626</t>
-  </si>
-  <si>
-    <t>LP-051803</t>
-  </si>
-  <si>
-    <t>LP-051801</t>
-  </si>
-  <si>
-    <t>LP-051381</t>
-  </si>
-  <si>
-    <t>LP-051703</t>
-  </si>
-  <si>
-    <t>LP-050422</t>
-  </si>
-  <si>
-    <t>LP-049475</t>
-  </si>
-  <si>
-    <t>LP-049096</t>
-  </si>
-  <si>
-    <t>LP-056406</t>
-  </si>
-  <si>
-    <t>LP-056226</t>
-  </si>
-  <si>
-    <t>LP-055345</t>
-  </si>
-  <si>
-    <t>LP-053413</t>
-  </si>
-  <si>
-    <t>LP-053215</t>
+    <t>LP-056391</t>
+  </si>
+  <si>
+    <t>LP-053103</t>
+  </si>
+  <si>
+    <t>LP-054538</t>
+  </si>
+  <si>
+    <t>LP-056845</t>
+  </si>
+  <si>
+    <t>LP-051365</t>
+  </si>
+  <si>
+    <t>LP-056117</t>
+  </si>
+  <si>
+    <t>LP-051399</t>
+  </si>
+  <si>
+    <t>LP-055504</t>
+  </si>
+  <si>
+    <t>LP-057557</t>
+  </si>
+  <si>
+    <t>LP-057373</t>
+  </si>
+  <si>
+    <t>LP-052979</t>
+  </si>
+  <si>
+    <t>LP-056323</t>
+  </si>
+  <si>
+    <t>LP-056262</t>
+  </si>
+  <si>
+    <t>LP-057764</t>
+  </si>
+  <si>
+    <t>LP-057043</t>
+  </si>
+  <si>
+    <t>LP-056522</t>
+  </si>
+  <si>
+    <t>LP-055819</t>
+  </si>
+  <si>
+    <t>LP-055170</t>
+  </si>
+  <si>
+    <t>LP-055661</t>
+  </si>
+  <si>
+    <t>LP-051148</t>
+  </si>
+  <si>
+    <t>LP-053036</t>
+  </si>
+  <si>
+    <t>LP-052913</t>
+  </si>
+  <si>
+    <t>LP-056770</t>
+  </si>
+  <si>
+    <t>LP-055667</t>
+  </si>
+  <si>
+    <t>LP-056608</t>
+  </si>
+  <si>
+    <t>LP-056831</t>
+  </si>
+  <si>
+    <t>LP-054822</t>
+  </si>
+  <si>
+    <t>LP-056511</t>
+  </si>
+  <si>
+    <t>LP-052768</t>
+  </si>
+  <si>
+    <t>LP-055201</t>
+  </si>
+  <si>
+    <t>LP-057371</t>
+  </si>
+  <si>
+    <t>LP-057372</t>
+  </si>
+  <si>
+    <t>LP-053935</t>
+  </si>
+  <si>
+    <t>LP-054831</t>
+  </si>
+  <si>
+    <t>LP-056836</t>
+  </si>
+  <si>
+    <t>LP-057949</t>
+  </si>
+  <si>
+    <t>LP-056397</t>
+  </si>
+  <si>
+    <t>LP-057340</t>
+  </si>
+  <si>
+    <t>LP-057936</t>
+  </si>
+  <si>
+    <t>LP-051145</t>
+  </si>
+  <si>
+    <t>LP-056328</t>
+  </si>
+  <si>
+    <t>LP-055674</t>
+  </si>
+  <si>
+    <t>LP-055177</t>
+  </si>
+  <si>
+    <t>LP-055737</t>
+  </si>
+  <si>
+    <t>LP-057541</t>
+  </si>
+  <si>
+    <t>LP-058186</t>
+  </si>
+  <si>
+    <t>LP-055176</t>
+  </si>
+  <si>
+    <t>LP-057218</t>
+  </si>
+  <si>
+    <t>LP-054926</t>
+  </si>
+  <si>
+    <t>LP-056452</t>
+  </si>
+  <si>
+    <t>LP-056321</t>
+  </si>
+  <si>
+    <t>LP-056960</t>
+  </si>
+  <si>
+    <t>LP-055342</t>
+  </si>
+  <si>
+    <t>LP-057214</t>
+  </si>
+  <si>
+    <t>LP-057125</t>
+  </si>
+  <si>
+    <t>LP-056719</t>
+  </si>
+  <si>
+    <t>LP-057760</t>
+  </si>
+  <si>
+    <t>LP-050411</t>
+  </si>
+  <si>
+    <t>LP-054611</t>
+  </si>
+  <si>
+    <t>LP-057166</t>
+  </si>
+  <si>
+    <t>LP-055182</t>
+  </si>
+  <si>
+    <t>LP-056537</t>
+  </si>
+  <si>
+    <t>LP-057374</t>
+  </si>
+  <si>
+    <t>LP-057539</t>
+  </si>
+  <si>
+    <t>LP-056881</t>
+  </si>
+  <si>
+    <t>LP-057337</t>
+  </si>
+  <si>
+    <t>LP-056607</t>
+  </si>
+  <si>
+    <t>LP-055337</t>
+  </si>
+  <si>
+    <t>LP-055325</t>
+  </si>
+  <si>
+    <t>LP-056526</t>
+  </si>
+  <si>
+    <t>LP-056224</t>
+  </si>
+  <si>
+    <t>LP-051055</t>
+  </si>
+  <si>
+    <t>LP-055324</t>
+  </si>
+  <si>
+    <t>LP-056008</t>
+  </si>
+  <si>
+    <t>LP-051050</t>
+  </si>
+  <si>
+    <t>LP-055364</t>
+  </si>
+  <si>
+    <t>LP-055074</t>
+  </si>
+  <si>
+    <t>LP-056841</t>
+  </si>
+  <si>
+    <t>LP-057341</t>
+  </si>
+  <si>
+    <t>LP-057763</t>
+  </si>
+  <si>
+    <t>LP-051692</t>
+  </si>
+  <si>
+    <t>LP-057537</t>
+  </si>
+  <si>
+    <t>LP-053402</t>
+  </si>
+  <si>
+    <t>LP-057937</t>
+  </si>
+  <si>
+    <t>LP-053608</t>
+  </si>
+  <si>
+    <t>LP-054579</t>
+  </si>
+  <si>
+    <t>LP-048756</t>
+  </si>
+  <si>
+    <t>LP-052950</t>
+  </si>
+  <si>
+    <t>LP-057701</t>
+  </si>
+  <si>
+    <t>LP-056399</t>
+  </si>
+  <si>
+    <t>LP-056578</t>
+  </si>
+  <si>
+    <t>LP-057545</t>
+  </si>
+  <si>
+    <t>LP-057624</t>
+  </si>
+  <si>
+    <t>LP-057622</t>
+  </si>
+  <si>
+    <t>LP-057623</t>
+  </si>
+  <si>
+    <t>LP-053934</t>
+  </si>
+  <si>
+    <t>LP-057449</t>
+  </si>
+  <si>
+    <t>LP-057339</t>
+  </si>
+  <si>
+    <t>LP-055698</t>
   </si>
 </sst>
 </file>
@@ -482,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -507,187 +684,482 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/99 - Excels/Open-LPs - pé.xlsx
+++ b/99 - Excels/Open-LPs - pé.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\99 - Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09A34087-F46E-4444-908A-F871187D3179}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{076BFC80-B6EE-4E66-8BDE-BCFF253DE0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,306 +20,198 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>LP</t>
   </si>
   <si>
-    <t>LP-056391</t>
-  </si>
-  <si>
-    <t>LP-053103</t>
-  </si>
-  <si>
-    <t>LP-054538</t>
-  </si>
-  <si>
-    <t>LP-056845</t>
-  </si>
-  <si>
-    <t>LP-051365</t>
-  </si>
-  <si>
-    <t>LP-056117</t>
-  </si>
-  <si>
-    <t>LP-051399</t>
-  </si>
-  <si>
-    <t>LP-055504</t>
-  </si>
-  <si>
-    <t>LP-057557</t>
-  </si>
-  <si>
-    <t>LP-057373</t>
-  </si>
-  <si>
-    <t>LP-052979</t>
-  </si>
-  <si>
-    <t>LP-056323</t>
-  </si>
-  <si>
-    <t>LP-056262</t>
-  </si>
-  <si>
-    <t>LP-057764</t>
-  </si>
-  <si>
-    <t>LP-057043</t>
-  </si>
-  <si>
-    <t>LP-056522</t>
-  </si>
-  <si>
-    <t>LP-055819</t>
-  </si>
-  <si>
-    <t>LP-055170</t>
-  </si>
-  <si>
-    <t>LP-055661</t>
-  </si>
-  <si>
-    <t>LP-051148</t>
-  </si>
-  <si>
-    <t>LP-053036</t>
-  </si>
-  <si>
-    <t>LP-052913</t>
-  </si>
-  <si>
-    <t>LP-056770</t>
-  </si>
-  <si>
-    <t>LP-055667</t>
-  </si>
-  <si>
-    <t>LP-056608</t>
-  </si>
-  <si>
-    <t>LP-056831</t>
-  </si>
-  <si>
-    <t>LP-054822</t>
-  </si>
-  <si>
-    <t>LP-056511</t>
-  </si>
-  <si>
-    <t>LP-052768</t>
-  </si>
-  <si>
-    <t>LP-055201</t>
-  </si>
-  <si>
-    <t>LP-057371</t>
-  </si>
-  <si>
-    <t>LP-057372</t>
-  </si>
-  <si>
-    <t>LP-053935</t>
-  </si>
-  <si>
-    <t>LP-054831</t>
-  </si>
-  <si>
-    <t>LP-056836</t>
-  </si>
-  <si>
-    <t>LP-057949</t>
-  </si>
-  <si>
-    <t>LP-056397</t>
-  </si>
-  <si>
-    <t>LP-057340</t>
-  </si>
-  <si>
-    <t>LP-057936</t>
-  </si>
-  <si>
-    <t>LP-051145</t>
-  </si>
-  <si>
-    <t>LP-056328</t>
-  </si>
-  <si>
-    <t>LP-055674</t>
-  </si>
-  <si>
-    <t>LP-055177</t>
-  </si>
-  <si>
-    <t>LP-055737</t>
-  </si>
-  <si>
-    <t>LP-057541</t>
-  </si>
-  <si>
-    <t>LP-058186</t>
-  </si>
-  <si>
-    <t>LP-055176</t>
-  </si>
-  <si>
-    <t>LP-057218</t>
-  </si>
-  <si>
-    <t>LP-054926</t>
-  </si>
-  <si>
-    <t>LP-056452</t>
-  </si>
-  <si>
-    <t>LP-056321</t>
-  </si>
-  <si>
-    <t>LP-056960</t>
-  </si>
-  <si>
-    <t>LP-055342</t>
-  </si>
-  <si>
-    <t>LP-057214</t>
-  </si>
-  <si>
-    <t>LP-057125</t>
-  </si>
-  <si>
-    <t>LP-056719</t>
-  </si>
-  <si>
-    <t>LP-057760</t>
-  </si>
-  <si>
-    <t>LP-050411</t>
-  </si>
-  <si>
-    <t>LP-054611</t>
-  </si>
-  <si>
-    <t>LP-057166</t>
-  </si>
-  <si>
-    <t>LP-055182</t>
-  </si>
-  <si>
-    <t>LP-056537</t>
-  </si>
-  <si>
-    <t>LP-057374</t>
-  </si>
-  <si>
-    <t>LP-057539</t>
-  </si>
-  <si>
-    <t>LP-056881</t>
-  </si>
-  <si>
-    <t>LP-057337</t>
-  </si>
-  <si>
-    <t>LP-056607</t>
-  </si>
-  <si>
-    <t>LP-055337</t>
-  </si>
-  <si>
-    <t>LP-055325</t>
-  </si>
-  <si>
-    <t>LP-056526</t>
-  </si>
-  <si>
-    <t>LP-056224</t>
-  </si>
-  <si>
-    <t>LP-051055</t>
-  </si>
-  <si>
-    <t>LP-055324</t>
-  </si>
-  <si>
-    <t>LP-056008</t>
-  </si>
-  <si>
-    <t>LP-051050</t>
-  </si>
-  <si>
-    <t>LP-055364</t>
-  </si>
-  <si>
-    <t>LP-055074</t>
-  </si>
-  <si>
-    <t>LP-056841</t>
-  </si>
-  <si>
-    <t>LP-057341</t>
-  </si>
-  <si>
-    <t>LP-057763</t>
-  </si>
-  <si>
-    <t>LP-051692</t>
-  </si>
-  <si>
-    <t>LP-057537</t>
-  </si>
-  <si>
-    <t>LP-053402</t>
-  </si>
-  <si>
-    <t>LP-057937</t>
-  </si>
-  <si>
-    <t>LP-053608</t>
-  </si>
-  <si>
-    <t>LP-054579</t>
-  </si>
-  <si>
-    <t>LP-048756</t>
-  </si>
-  <si>
-    <t>LP-052950</t>
-  </si>
-  <si>
-    <t>LP-057701</t>
-  </si>
-  <si>
-    <t>LP-056399</t>
-  </si>
-  <si>
-    <t>LP-056578</t>
-  </si>
-  <si>
-    <t>LP-057545</t>
-  </si>
-  <si>
-    <t>LP-057624</t>
-  </si>
-  <si>
-    <t>LP-057622</t>
-  </si>
-  <si>
-    <t>LP-057623</t>
-  </si>
-  <si>
-    <t>LP-053934</t>
-  </si>
-  <si>
-    <t>LP-057449</t>
-  </si>
-  <si>
-    <t>LP-057339</t>
-  </si>
-  <si>
-    <t>LP-055698</t>
+    <t>LP-044722</t>
+  </si>
+  <si>
+    <t>LP-047645</t>
+  </si>
+  <si>
+    <t>LP-049330</t>
+  </si>
+  <si>
+    <t>LP-050124</t>
+  </si>
+  <si>
+    <t>LP-052989</t>
+  </si>
+  <si>
+    <t>LP-053261</t>
+  </si>
+  <si>
+    <t>LP-053306</t>
+  </si>
+  <si>
+    <t>LP-055343</t>
+  </si>
+  <si>
+    <t>LP-055736</t>
+  </si>
+  <si>
+    <t>LP-055745</t>
+  </si>
+  <si>
+    <t>LP-055760</t>
+  </si>
+  <si>
+    <t>LP-055793</t>
+  </si>
+  <si>
+    <t>LP-056089</t>
+  </si>
+  <si>
+    <t>LP-056223</t>
+  </si>
+  <si>
+    <t>LP-056324</t>
+  </si>
+  <si>
+    <t>LP-056377</t>
+  </si>
+  <si>
+    <t>LP-056384</t>
+  </si>
+  <si>
+    <t>LP-056454</t>
+  </si>
+  <si>
+    <t>LP-056486</t>
+  </si>
+  <si>
+    <t>LP-056520</t>
+  </si>
+  <si>
+    <t>LP-056521</t>
+  </si>
+  <si>
+    <t>LP-056536</t>
+  </si>
+  <si>
+    <t>LP-056975</t>
+  </si>
+  <si>
+    <t>LP-056987</t>
+  </si>
+  <si>
+    <t>LP-057093</t>
+  </si>
+  <si>
+    <t>LP-057117</t>
+  </si>
+  <si>
+    <t>LP-057378</t>
+  </si>
+  <si>
+    <t>LP-057422</t>
+  </si>
+  <si>
+    <t>LP-057538</t>
+  </si>
+  <si>
+    <t>LP-057686</t>
+  </si>
+  <si>
+    <t>LP-057699</t>
+  </si>
+  <si>
+    <t>LP-057757</t>
+  </si>
+  <si>
+    <t>LP-057762</t>
+  </si>
+  <si>
+    <t>LP-057875</t>
+  </si>
+  <si>
+    <t>LP-057876</t>
+  </si>
+  <si>
+    <t>LP-057982</t>
+  </si>
+  <si>
+    <t>LP-057983</t>
+  </si>
+  <si>
+    <t>LP-057984</t>
+  </si>
+  <si>
+    <t>LP-057986</t>
+  </si>
+  <si>
+    <t>LP-057993</t>
+  </si>
+  <si>
+    <t>LP-058232</t>
+  </si>
+  <si>
+    <t>LP-058233</t>
+  </si>
+  <si>
+    <t>LP-058238</t>
+  </si>
+  <si>
+    <t>LP-058244</t>
+  </si>
+  <si>
+    <t>LP-051721</t>
+  </si>
+  <si>
+    <t>LP-052910</t>
+  </si>
+  <si>
+    <t>LP-055346</t>
+  </si>
+  <si>
+    <t>LP-055496</t>
+  </si>
+  <si>
+    <t>LP-055675</t>
+  </si>
+  <si>
+    <t>LP-055765</t>
+  </si>
+  <si>
+    <t>LP-056263</t>
+  </si>
+  <si>
+    <t>LP-056398</t>
+  </si>
+  <si>
+    <t>LP-056579</t>
+  </si>
+  <si>
+    <t>LP-056901</t>
+  </si>
+  <si>
+    <t>LP-057002</t>
+  </si>
+  <si>
+    <t>LP-057338</t>
+  </si>
+  <si>
+    <t>LP-057700</t>
+  </si>
+  <si>
+    <t>LP-057729</t>
+  </si>
+  <si>
+    <t>LP-057730</t>
+  </si>
+  <si>
+    <t>LP-057827</t>
+  </si>
+  <si>
+    <t>LP-057894</t>
+  </si>
+  <si>
+    <t>LP-057964</t>
+  </si>
+  <si>
+    <t>LP-058236</t>
   </si>
 </sst>
 </file>
@@ -659,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -689,477 +581,297 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
